--- a/CoreEngine/GameData/Test__npm__/CSV__npm__/TestRefereceTable.xlsx
+++ b/CoreEngine/GameData/Test__npm__/CSV__npm__/TestRefereceTable.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\CoreFramework Develop\Assets\_WorkSpace\CoreFramework\CoreEngine\GameData\Test\CSV\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\CoreFramework Develop\Assets\_WorkSpace\CoreFramework\CoreEngine\GameData\Test__npm__\CSV__npm__\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5474C52D-9934-4B9B-A146-A35D49F1EEDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F52CEC7E-E7E5-472B-A932-4E4CF3A5300B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -588,7 +588,7 @@
         <v>28</v>
       </c>
       <c r="B6" s="2">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2">
         <v>1005</v>
